--- a/Project_ETF/ETF_Investment_Portfolio/009805/ETF_Investment_Portfolio_20260901.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/009805/ETF_Investment_Portfolio_20260901.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D71"/>
+  <dimension ref="A1:D72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24.75" customWidth="1" min="1" max="1"/>
@@ -611,12 +611,12 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>76,907</t>
+          <t>77,907</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>10.94%</t>
+          <t>10.68%</t>
         </is>
       </c>
     </row>
@@ -633,12 +633,12 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>31,796</t>
+          <t>32,296</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>10.11%</t>
+          <t>10.18%</t>
         </is>
       </c>
     </row>
@@ -655,12 +655,12 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>89,125</t>
+          <t>90,525</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>8.16%</t>
+          <t>8.13%</t>
         </is>
       </c>
     </row>
@@ -677,12 +677,12 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>35,055</t>
+          <t>35,555</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>7.53%</t>
+          <t>7.63%</t>
         </is>
       </c>
     </row>
@@ -699,12 +699,12 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>192,556</t>
+          <t>195,556</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>5.61%</t>
+          <t>5.69%</t>
         </is>
       </c>
     </row>
@@ -721,12 +721,12 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>102,391</t>
+          <t>103,991</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>4.35%</t>
+          <t>4.39%</t>
         </is>
       </c>
     </row>
@@ -743,12 +743,12 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>48,295</t>
+          <t>49,095</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.53%</t>
+          <t>3.68%</t>
         </is>
       </c>
     </row>
@@ -765,12 +765,12 @@
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>111,066</t>
+          <t>112,766</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.46%</t>
+          <t>3.49%</t>
         </is>
       </c>
     </row>
@@ -787,12 +787,12 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>58,159</t>
+          <t>59,059</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.10%</t>
+          <t>3.05%</t>
         </is>
       </c>
     </row>
@@ -809,12 +809,12 @@
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>19,079</t>
+          <t>19,379</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>3.06%</t>
+          <t>3.01%</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>115,483</t>
+          <t>117,283</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.70%</t>
+          <t>2.73%</t>
         </is>
       </c>
     </row>
@@ -853,12 +853,12 @@
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>53,527</t>
+          <t>54,327</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.32%</t>
+          <t>2.34%</t>
         </is>
       </c>
     </row>
@@ -875,12 +875,12 @@
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>22,231</t>
+          <t>22,531</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.16%</t>
+          <t>2.22%</t>
         </is>
       </c>
     </row>
@@ -897,12 +897,12 @@
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>134,501</t>
+          <t>136,601</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.08%</t>
+          <t>2.10%</t>
         </is>
       </c>
     </row>
@@ -919,12 +919,12 @@
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>23,904</t>
+          <t>24,304</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>1.71%</t>
+          <t>1.70%</t>
         </is>
       </c>
     </row>
@@ -941,12 +941,12 @@
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>61,403</t>
+          <t>62,403</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>1.65%</t>
+          <t>1.66%</t>
         </is>
       </c>
     </row>
@@ -963,12 +963,12 @@
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>36,280</t>
+          <t>36,780</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1.37%</t>
+          <t>1.39%</t>
         </is>
       </c>
     </row>
@@ -985,12 +985,12 @@
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>49,036</t>
+          <t>49,836</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>1.27%</t>
+          <t>1.28%</t>
         </is>
       </c>
     </row>
@@ -1007,12 +1007,12 @@
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>76,001</t>
+          <t>77,101</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.23%</t>
+          <t>1.25%</t>
         </is>
       </c>
     </row>
@@ -1029,56 +1029,56 @@
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>49,360</t>
+          <t>50,160</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>1.23%</t>
+          <t>1.24%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>TTEK UW</t>
+          <t>WEC US</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>德照科技公司</t>
+          <t>WEC能源集團公司</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>93,763</t>
+          <t>32,510</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>1.20%</t>
+          <t>1.21%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>WEC US</t>
+          <t>TTEK UW</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>WEC能源集團公司</t>
+          <t>德照科技公司</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>32,010</t>
+          <t>95,263</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>1.20%</t>
+          <t>1.19%</t>
         </is>
       </c>
     </row>
@@ -1095,12 +1095,12 @@
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>30,045</t>
+          <t>30,445</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>1.13%</t>
+          <t>1.14%</t>
         </is>
       </c>
     </row>
@@ -1117,12 +1117,12 @@
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>46,327</t>
+          <t>47,127</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>1.11%</t>
+          <t>1.10%</t>
         </is>
       </c>
     </row>
@@ -1139,78 +1139,78 @@
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>21,958</t>
+          <t>22,258</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>1.07%</t>
+          <t>1.08%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>AEE US</t>
+          <t>EIX US</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>阿莫林公司</t>
+          <t>愛迪生國際</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>27,169</t>
+          <t>51,310</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.02%</t>
+          <t>1.06%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>DTE US</t>
+          <t>AEE US</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>DTE能源</t>
+          <t>阿莫林公司</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>20,409</t>
+          <t>27,569</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>0.98%</t>
+          <t>1.03%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>EIX US</t>
+          <t>DTE US</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>愛迪生國際</t>
+          <t>DTE能源</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>50,510</t>
+          <t>20,709</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>0.97%</t>
+          <t>0.99%</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>11,137</t>
+          <t>11,337</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -1249,12 +1249,12 @@
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>74,074</t>
+          <t>75,174</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>0.90%</t>
+          <t>0.91%</t>
         </is>
       </c>
     </row>
@@ -1271,56 +1271,56 @@
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>29,914</t>
+          <t>30,314</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>0.86%</t>
+          <t>0.87%</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>AEIS US</t>
+          <t>ENS US</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>艾儀有限公司</t>
+          <t>EnerSys</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>8,804</t>
+          <t>13,252</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.86%</t>
+          <t>0.84%</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>ENS US</t>
+          <t>AEIS US</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>EnerSys</t>
+          <t>艾儀有限公司</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>13,052</t>
+          <t>9,004</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>0.85%</t>
+          <t>0.84%</t>
         </is>
       </c>
     </row>
@@ -1342,24 +1342,24 @@
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>0.82%</t>
+          <t>0.80%</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>AGX US</t>
+          <t>CMS US</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>阿根公司</t>
+          <t>CMS能源</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>4,821</t>
+          <t>30,691</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
@@ -1371,61 +1371,61 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>CMS US</t>
+          <t>PCG US</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>CMS能源</t>
+          <t>太平洋電力瓦斯公司</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>30,291</t>
+          <t>146,245</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>0.73%</t>
+          <t>0.72%</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>GNRC US</t>
+          <t>AGX US</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>基內瑞克控股公司</t>
+          <t>阿根公司</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>10,446</t>
+          <t>4,921</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>0.69%</t>
+          <t>0.70%</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>PCG US</t>
+          <t>GNRC US</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>太平洋電力瓦斯公司</t>
+          <t>基內瑞克控股公司</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>144,045</t>
+          <t>10,646</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>25,381</t>
+          <t>25,781</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>42,883</t>
+          <t>43,583</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>15,827</t>
+          <t>16,127</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>13,224</t>
+          <t>13,424</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
@@ -1535,7 +1535,7 @@
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>93,202</t>
+          <t>94,702</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
@@ -1557,56 +1557,56 @@
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>6,727</t>
+          <t>6,827</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>0.43%</t>
+          <t>0.41%</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>VICR US</t>
+          <t>MYRG US</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>懷克爾公司</t>
+          <t>MYR集團公司</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>5,778</t>
+          <t>3,651</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>0.38%</t>
+          <t>0.37%</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>MYRG US</t>
+          <t>VICR US</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>MYR集團公司</t>
+          <t>懷克爾公司</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>3,551</t>
+          <t>5,878</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>0.37%</t>
+          <t>0.36%</t>
         </is>
       </c>
     </row>
@@ -1623,12 +1623,12 @@
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>23,119</t>
+          <t>23,519</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.29%</t>
         </is>
       </c>
     </row>
@@ -1645,7 +1645,7 @@
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>7,821</t>
+          <t>8,021</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
@@ -1667,7 +1667,7 @@
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>2,739</t>
+          <t>2,839</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
@@ -1689,7 +1689,7 @@
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>18,153</t>
+          <t>18,453</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>37,761</t>
+          <t>38,261</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
@@ -1719,6 +1719,20 @@
           <t>0.01%</t>
         </is>
       </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>C_NTD</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr"/>
+      <c r="C72" s="4" t="inlineStr">
+        <is>
+          <t>118,269,468</t>
+        </is>
+      </c>
+      <c r="D72" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="5">
